--- a/data/trans_orig/P36BPD11_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD11_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que consumen repostería comercial a la semana en 2023</t>
+          <t>Población según el número de veces que consumen repostería comercial a la semana en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>215470</t>
+          <t>215505</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>259259</t>
+          <t>257233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>345448</t>
+          <t>343829</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>386227</t>
+          <t>388169</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>574608</t>
+          <t>571854</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>634087</t>
+          <t>631618</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,87%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>158361</t>
+          <t>157780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>197521</t>
+          <t>197919</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252514</t>
+          <t>252291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>293062</t>
+          <t>291311</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>423538</t>
+          <t>419601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>478101</t>
+          <t>476707</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82873</t>
+          <t>82542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118137</t>
+          <t>118696</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>99968</t>
+          <t>100676</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>131015</t>
+          <t>132160</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>191061</t>
+          <t>192599</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>237907</t>
+          <t>241129</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>946079</t>
+          <t>950819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1471451</t>
+          <t>1515333</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>946162</t>
+          <t>937743</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1424020</t>
+          <t>1400217</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1945895</t>
+          <t>1947620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2613994</t>
+          <t>2696943</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>564434</t>
+          <t>525465</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>908092</t>
+          <t>910892</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,82 +1314,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>39,79%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1052</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>810546</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>588942</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>941850</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>36,23%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>26,33%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>42,1%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>1605663</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>1286983</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>1795485</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>35,48%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>28,43%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>39,67%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1052</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>810546</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>606769</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>943949</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>36,23%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>27,12%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>42,2%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1605663</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1312971</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1793936</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>35,48%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>29,01%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>269403</t>
+          <t>259564</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>455755</t>
+          <t>449877</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>250328</t>
+          <t>255868</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>425566</t>
+          <t>424538</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>589383</t>
+          <t>579101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>830978</t>
+          <t>828814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>332303</t>
+          <t>330340</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>386278</t>
+          <t>386118</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>369248</t>
+          <t>370602</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>413990</t>
+          <t>415679</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>715428</t>
+          <t>714697</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>783398</t>
+          <t>784843</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,13%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>184791</t>
+          <t>183410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>235375</t>
+          <t>232945</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172128</t>
+          <t>170896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>214438</t>
+          <t>214254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>370832</t>
+          <t>369879</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>436553</t>
+          <t>437161</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63034</t>
+          <t>62188</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100260</t>
+          <t>99849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61377</t>
+          <t>60598</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90204</t>
+          <t>90308</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132635</t>
+          <t>132003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179503</t>
+          <t>176560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1548382</t>
+          <t>1558918</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2079584</t>
+          <t>2119406</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1705759</t>
+          <t>1703963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2211370</t>
+          <t>2187904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3316618</t>
+          <t>3296890</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4011313</t>
+          <t>4016815</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,59%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>939077</t>
+          <t>907239</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1297415</t>
+          <t>1287582</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1054960</t>
+          <t>1063999</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1395162</t>
+          <t>1414242</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2152778</t>
+          <t>2103817</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2654853</t>
+          <t>2647203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>437625</t>
+          <t>427658</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>633913</t>
+          <t>631538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>443560</t>
+          <t>445809</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>620763</t>
+          <t>617645</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>949248</t>
+          <t>955143</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1200597</t>
+          <t>1204922</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD11_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD11_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>237628</t>
+          <t>276351</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>215505</t>
+          <t>253111</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>257233</t>
+          <t>299451</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>365656</t>
+          <t>389918</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>343829</t>
+          <t>371182</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>388169</t>
+          <t>413954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>603285</t>
+          <t>666268</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>571854</t>
+          <t>635984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>631618</t>
+          <t>697241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>177821</t>
+          <t>197020</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>157780</t>
+          <t>175935</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>197919</t>
+          <t>220269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>272057</t>
+          <t>303424</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252291</t>
+          <t>281246</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291311</t>
+          <t>323456</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>449877</t>
+          <t>500444</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>419601</t>
+          <t>471235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>476707</t>
+          <t>531884</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>98031</t>
+          <t>103577</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82542</t>
+          <t>86376</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118696</t>
+          <t>123342</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>115353</t>
+          <t>126100</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100676</t>
+          <t>110735</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>132160</t>
+          <t>145034</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>213384</t>
+          <t>229678</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>192599</t>
+          <t>205315</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>241129</t>
+          <t>253836</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>513480</t>
+          <t>576948</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>513480</t>
+          <t>576948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>513480</t>
+          <t>576948</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>753066</t>
+          <t>819442</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>753066</t>
+          <t>819442</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>753066</t>
+          <t>819442</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1266546</t>
+          <t>1396390</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1266546</t>
+          <t>1396390</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1266546</t>
+          <t>1396390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1108032</t>
+          <t>947371</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>950819</t>
+          <t>894064</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1515333</t>
+          <t>999354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1088447</t>
+          <t>989195</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>937743</t>
+          <t>947919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1400217</t>
+          <t>1034773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2196479</t>
+          <t>1936565</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1947620</t>
+          <t>1866077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2696943</t>
+          <t>1999938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>45,47%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>795117</t>
+          <t>851485</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>525465</t>
+          <t>801586</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>910892</t>
+          <t>903706</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>810546</t>
+          <t>826065</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>588942</t>
+          <t>783155</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>941850</t>
+          <t>871181</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1605663</t>
+          <t>1677550</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1286983</t>
+          <t>1615204</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1795485</t>
+          <t>1748546</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,75%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>385984</t>
+          <t>429011</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>259564</t>
+          <t>383796</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>449877</t>
+          <t>475215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>337973</t>
+          <t>355226</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>255868</t>
+          <t>321459</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>424538</t>
+          <t>389685</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>723958</t>
+          <t>784237</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>579101</t>
+          <t>732092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>828814</t>
+          <t>844904</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2289133</t>
+          <t>2227867</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2289133</t>
+          <t>2227867</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2289133</t>
+          <t>2227867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2236967</t>
+          <t>2170486</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2236967</t>
+          <t>2170486</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2236967</t>
+          <t>2170486</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4526100</t>
+          <t>4398352</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4526100</t>
+          <t>4398352</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4526100</t>
+          <t>4398352</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,62 +1637,62 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>358389</t>
+          <t>391190</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>330340</t>
+          <t>363816</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>386118</t>
+          <t>420396</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>59,08%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>437584</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>413344</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>462571</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>59,71%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>391649</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>370602</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>415679</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>59,47%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>750038</t>
+          <t>828774</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>714697</t>
+          <t>789884</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>784843</t>
+          <t>861598</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,65%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>208844</t>
+          <t>231100</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>183410</t>
+          <t>204799</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>232945</t>
+          <t>257569</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>192641</t>
+          <t>211123</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>170896</t>
+          <t>189761</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>214254</t>
+          <t>234142</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>401485</t>
+          <t>442223</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>369879</t>
+          <t>410581</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>437161</t>
+          <t>479803</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>79390</t>
+          <t>89297</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62188</t>
+          <t>69986</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99849</t>
+          <t>112490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>74266</t>
+          <t>84153</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60598</t>
+          <t>68710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90308</t>
+          <t>102622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>153656</t>
+          <t>173450</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132003</t>
+          <t>151302</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176560</t>
+          <t>201605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>658555</t>
+          <t>732860</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>658555</t>
+          <t>732860</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>658555</t>
+          <t>732860</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1305178</t>
+          <t>1444447</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1305178</t>
+          <t>1444447</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1305178</t>
+          <t>1444447</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1704050</t>
+          <t>1614911</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1558918</t>
+          <t>1558425</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2119406</t>
+          <t>1685204</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1845752</t>
+          <t>1816696</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1703963</t>
+          <t>1763065</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2187904</t>
+          <t>1871759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3549801</t>
+          <t>3431608</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3296890</t>
+          <t>3351447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4016815</t>
+          <t>3519301</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>48,61%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1181782</t>
+          <t>1279606</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>907239</t>
+          <t>1220466</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1287582</t>
+          <t>1338013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1275244</t>
+          <t>1340612</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1063999</t>
+          <t>1287880</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1414242</t>
+          <t>1390905</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2457025</t>
+          <t>2620218</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2103817</t>
+          <t>2533483</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2647203</t>
+          <t>2695792</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -2319,69 +2319,69 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>563406</t>
+          <t>621885</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>427658</t>
+          <t>571031</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>631538</t>
+          <t>672648</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>17,69%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>19,13%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>565479</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>526532</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>607848</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>14,14%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>16,33%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>12,4%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,31%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>527592</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>445809</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>617645</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>12,22%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>16,93%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>1324</t>
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1090997</t>
+          <t>1187364</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>955143</t>
+          <t>1120447</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1204922</t>
+          <t>1247099</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3449237</t>
+          <t>3516402</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3449237</t>
+          <t>3516402</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3449237</t>
+          <t>3516402</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3648588</t>
+          <t>3722787</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3648588</t>
+          <t>3722787</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3648588</t>
+          <t>3722787</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7097824</t>
+          <t>7239190</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7097824</t>
+          <t>7239190</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7097824</t>
+          <t>7239190</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
